--- a/y12901/长上下文截断审计/demo_output/审计报告.xlsx
+++ b/y12901/长上下文截断审计/demo_output/审计报告.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名词说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'详细记录'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'详细记录'!$A$1:$J$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,9 @@
     </font>
     <font>
       <color rgb="009C5700"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -108,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,16 +125,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -500,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -526,7 +532,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:20:11</t>
+          <t>2026-06-17 16:30:51</t>
         </is>
       </c>
     </row>
@@ -537,7 +543,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +553,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -584,11 +590,21 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>人工截断标记</t>
+          <t>输入本身不完整</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>工具调用参数错误</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -606,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -676,55 +692,55 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>REC-004</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>REC-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>人工截断标记</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>人工复核判断：输入不完整</t>
+          <t>未截断</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>未检测到截断迹象</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>382</v>
+        <v>150</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>385</v>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>中（部分影响）</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>群反馈补充</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>实际是文档没写完就提交了，不是系统截断的，属于输入本身不完整</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>产品需求文档：用户中心改版v2.0一、项目背景当前用户中心页面功能分散，用户找信息困难，客服咨询量居高不下。二、改版目标1. 提升用户自助解决问题的比例，降低客服工单量30%；2. 优化页面布局，提升...</t>
+        <v>146</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>低（轻微影响）</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>旧表</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>已审核</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>用户反馈订单系统在大促期间响应变慢，需要排查数据库查询性能。经过初步分析，发现订单表数据量已超过5000万条，部分查询没有走索引。建议：1. 对常用查询字段建立联合索引；2. 考虑分库分表方案；3. ...</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>REC-006</t>
+          <t>REC-002</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -734,45 +750,41 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>人工截断标记</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>人工复核判断：不截断</t>
+          <t>未截断</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>文本中存在单位不明确的数值，可能影响理解</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>223</v>
+        <v>290</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>中（部分影响）</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>群反馈补充</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>数据量单位明确（条），之前标注有误，这条不算截断</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>客户投诉处理记录客户名称：某某科技有限公司投诉时间：2024-03-15投诉内容：系统在处理批量数据导入时经常超时，数据量大约有5万条左右的时候就不行了。处理过程：1. 接到投诉后立即排查日志，发现是...</t>
+          <t>低（轻微影响）</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>旧表</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>关于用户增长策略的分析报告：一、当前用户现状：月活用户约500万，日活约200万，留存率30天约35%。二、增长渠道分析：1. 自然流量占比40%，主要来自搜索和口碑传播；2. 付费推广占比35%，包...</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>REC-009</t>
+          <t>REC-003</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -782,187 +794,467 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>人工截断标记</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>人工复核判断：不截断</t>
+          <t>未截断</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>未检测到截断迹象</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>266</v>
+        <v>347</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>267</v>
+        <v>377</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>中（部分影响）</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>群反馈补充</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>这条是完整的，不需要标记截断</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>【紧急】线上故障报告故障时间：2024-03-10 14:30-16:45故障影响：支付系统异常，约30%的用户下单失败故障原因：数据库主库连接池耗尽，导致请求排队故障处理过程：1. 14:35 收到...</t>
+          <t>低（轻微影响）</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>旧表</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>内容较长注意检查</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>技术架构升级方案背景：当前系统采用单体架构，随着业务快速发展，出现以下问题：1. 代码耦合度高，维护成本大；2. 发布效率低，一次全量发布需要2小时；3. 扩展性差，高峰期只能整体扩容。目标：用6个月...</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>REC-010</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>REC-004</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>单位不明确</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>人工复核判断：不截断</t>
+          <t>输入本身不完整</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>人工复核判断：输入不完整</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>309</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>低（轻微影响）</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
+        <v>385</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>中（部分影响）</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>群反馈补充</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>内容完整</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>项目复盘：一季度产品迭代整体情况概述：一季度共完成了12个需求的迭代交付，其中重点项目有3个，分别是用户中心改版、营销工具升级、数据看板一期。整体交付率85%，延期项目主要集中在数据相关的需求。存在的...</t>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>实际是文档没写完就提交了，不是系统截断的，属于输入本身不完整</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>产品需求文档：用户中心改版v2.0一、项目背景当前用户中心页面功能分散，用户找信息困难，客服咨询量居高不下。二、改版目标1. 提升用户自助解决问题的比例，降低客服工单量30%；2. 优化页面布局，提升...</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>REC-011</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>REC-005</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>人工截断标记</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>人工复核判断：截断-工具调用错误</t>
+          <t>未截断</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>文本中存在单位不明确的数值，可能影响理解</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>中（部分影响）</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>群反馈补充</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>工具调用参数错误导致内容处理失败，算截断</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>工具调用异常记录工具名称：search_codebase调用时间：2024-03-12 10:23:45错误信息：参数 query 类型错误，期望 string 实际收到 number请求参数：que...</t>
+        <v>157</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>低（轻微影响）</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>旧表</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>本周工作汇报：1. 完成用户登录模块的重构，修复了3个历史bug；2. 参与技术方案评审，输出评审意见5条；3. 协助新人熟悉项目，解答问题约10个；4. 处理线上告警2次，都是磁盘空间不足的问题。下...</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>REC-006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>未截断</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>人工复核判断：不截断</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>235</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>中（部分影响）</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>群反馈补充</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>数据量单位明确（条），之前标注有误，这条不算截断</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>客户投诉处理记录客户名称：某某科技有限公司投诉时间：2024-03-15投诉内容：系统在处理批量数据导入时经常超时，数据量大约有5万条左右的时候就不行了。处理过程：1. 接到投诉后立即排查日志，发现是...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>REC-007</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>输入本身不完整</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>输入内容为空或只有空白字符</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>高（影响使用）</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>旧表</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>空数据</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>REC-008</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>输入本身不完整</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>输入内容为空或只有空白字符</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>高（影响使用）</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>旧表</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>只有空格</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>REC-009</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>未截断</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>人工复核判断：不截断</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>266</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>267</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>中（部分影响）</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>群反馈补充</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>这条是完整的，不需要标记截断</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>【紧急】线上故障报告故障时间：2024-03-10 14:30-16:45故障影响：支付系统异常，约30%的用户下单失败故障原因：数据库主库连接池耗尽，导致请求排队故障处理过程：1. 14:35 收到...</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>REC-010</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>未截断</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>人工复核判断：不截断</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>302</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>309</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>低（轻微影响）</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>群反馈补充</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>内容完整</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>项目复盘：一季度产品迭代整体情况概述：一季度共完成了12个需求的迭代交付，其中重点项目有3个，分别是用户中心改版、营销工具升级、数据看板一期。整体交付率85%，延期项目主要集中在数据相关的需求。存在的...</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>REC-011</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>工具调用参数错误</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>人工复核判断：截断-工具调用错误</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>171</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>中（部分影响）</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>群反馈补充</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>工具调用参数错误导致内容处理失败，算截断</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>工具调用异常记录工具名称：search_codebase调用时间：2024-03-12 10:23:45错误信息：参数 query 类型错误，期望 string 实际收到 number请求参数：que...</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>REC-012</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>人工截断标记</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>未截断</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>人工复核判断：不截断-特殊场景</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E13" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F13" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>中（部分影响）</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>群反馈补充</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>模板空字段太多，但这是模板不算截断吧？</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>数据分析报告模板一、数据概览总用户数：付费用户数：活跃度：留存率：二、用户画像性别分布：年龄分布：地域分布：三、行为特征访问频次：停留时长：转化路径：四、结论与建议1.2.3.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -981,7 +1273,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>名词说明</t>
         </is>
@@ -993,7 +1285,7 @@
           <t>截断原因</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -1005,7 +1297,7 @@
           <t>token超限</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>输入的文字转换成token后，数量超过了模型的限制，导致后面的内容被切掉</t>
         </is>
@@ -1017,7 +1309,7 @@
           <t>上下文窗口不足</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>输入内容太长，快接近模型能处理的最大长度了，可能会被截断</t>
         </is>
@@ -1029,7 +1321,7 @@
           <t>工具调用参数错误</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>在调用工具时参数传错了格式，导致内容处理失败</t>
         </is>
@@ -1041,7 +1333,7 @@
           <t>人工截断标记</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>人工在备注里标注了这是截断的或者不完整的内容</t>
         </is>
@@ -1053,7 +1345,7 @@
           <t>输入本身不完整</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>原始数据就是空的或者缺内容</t>
         </is>
@@ -1065,7 +1357,7 @@
           <t>关键字段缺失</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>数据里缺少了应该有的字段信息</t>
         </is>
@@ -1077,7 +1369,7 @@
           <t>单位不明确</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>数值后面没有写清楚单位，可能造成理解偏差</t>
         </is>
@@ -1089,7 +1381,7 @@
           <t>未知原因</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>检测到有截断迹象，但具体原因不确定</t>
         </is>
